--- a/doc/docs/planilha_base_mapa.xlsx
+++ b/doc/docs/planilha_base_mapa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github_corrigido_dashboard_obrasdinamico\github\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCFF995-9770-4685-8FB4-A2A5EF8D83C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06CC311A-5D85-4D5F-B548-ADAB37F513D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEIA-ME" sheetId="1" r:id="rId1"/>
@@ -18165,6 +18165,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R388"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -18228,7 +18229,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -18278,7 +18279,7 @@
         <v>-46.416253400000002</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -18328,7 +18329,7 @@
         <v>-46.416704099999997</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -18378,7 +18379,7 @@
         <v>-46.417190099999999</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -18428,7 +18429,7 @@
         <v>-46.417341</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -18478,7 +18479,7 @@
         <v>-46.417501700000003</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -18528,7 +18529,7 @@
         <v>-46.4176821</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -18578,7 +18579,7 @@
         <v>-46.417981300000001</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -18628,7 +18629,7 @@
         <v>-46.418407199999997</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -18678,7 +18679,7 @@
         <v>-46.418206699999999</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -18728,7 +18729,7 @@
         <v>-46.4180463</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -18778,7 +18779,7 @@
         <v>-46.418264100000002</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -18828,7 +18829,7 @@
         <v>-46.4183649</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -18878,7 +18879,7 @@
         <v>-46.418435899999999</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -18928,7 +18929,7 @@
         <v>-46.416806899999997</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -18978,7 +18979,7 @@
         <v>-46.416913999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -19028,7 +19029,7 @@
         <v>-46.416511399999997</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -19078,7 +19079,7 @@
         <v>-46.416153399999999</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -19128,7 +19129,7 @@
         <v>-46.416207999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -19178,7 +19179,7 @@
         <v>-46.416177500000003</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -19228,7 +19229,7 @@
         <v>-46.418407199999997</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -19278,7 +19279,7 @@
         <v>-46.418435299999999</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -19328,7 +19329,7 @@
         <v>-46.416253400000002</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -19378,7 +19379,7 @@
         <v>-46.416341899999999</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -19428,7 +19429,7 @@
         <v>-46.416704099999997</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -19478,7 +19479,7 @@
         <v>-46.415709800000002</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -19528,7 +19529,7 @@
         <v>-46.415711799999997</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -19578,7 +19579,7 @@
         <v>-46.416806899999997</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -19628,7 +19629,7 @@
         <v>-46.416340599999998</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -19678,7 +19679,7 @@
         <v>-46.416158799999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -19728,7 +19729,7 @@
         <v>-46.416158799999998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -19778,7 +19779,7 @@
         <v>-46.416511399999997</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -19828,7 +19829,7 @@
         <v>-46.38594079802948</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -19878,7 +19879,7 @@
         <v>-46.386535748682967</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -19928,7 +19929,7 @@
         <v>-46.385331250405009</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>79</v>
       </c>
@@ -19978,7 +19979,7 @@
         <v>-46.385209892569947</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -20446,7 +20447,7 @@
         <v>530</v>
       </c>
       <c r="I45">
-        <v>120.49</v>
+        <v>0</v>
       </c>
       <c r="J45">
         <v>8.2200000000000006</v>
@@ -20502,7 +20503,7 @@
         <v>530</v>
       </c>
       <c r="I46">
-        <v>78.569999999999993</v>
+        <v>0</v>
       </c>
       <c r="J46">
         <v>8.16</v>
@@ -20588,7 +20589,7 @@
         <v>-46.401313100000003</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>117</v>
       </c>
@@ -20644,7 +20645,7 @@
         <v>-46.4176511</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>117</v>
       </c>
@@ -20700,7 +20701,7 @@
         <v>-46.417446300000002</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>117</v>
       </c>
@@ -20756,7 +20757,7 @@
         <v>-46.417286599999997</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>117</v>
       </c>
@@ -20812,7 +20813,7 @@
         <v>-46.418029900000001</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>117</v>
       </c>
@@ -20868,7 +20869,7 @@
         <v>-46.417090700000003</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -20924,7 +20925,7 @@
         <v>-46.416909699999998</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>117</v>
       </c>
@@ -20980,7 +20981,7 @@
         <v>-46.416524600000002</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>117</v>
       </c>
@@ -21036,7 +21037,7 @@
         <v>-46.416342700000001</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>117</v>
       </c>
@@ -21092,7 +21093,7 @@
         <v>-46.416342700000001</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>117</v>
       </c>
@@ -21148,7 +21149,7 @@
         <v>-46.4159948</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>117</v>
       </c>
@@ -21204,7 +21205,7 @@
         <v>-46.415814900000001</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>117</v>
       </c>
@@ -21260,7 +21261,7 @@
         <v>-46.415814900000001</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>117</v>
       </c>
@@ -21316,7 +21317,7 @@
         <v>-46.415630399999998</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>117</v>
       </c>
@@ -21372,7 +21373,7 @@
         <v>-46.4153284</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>117</v>
       </c>
@@ -21428,7 +21429,7 @@
         <v>-46.414648700000001</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>117</v>
       </c>
@@ -21484,7 +21485,7 @@
         <v>-46.415173099999997</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>117</v>
       </c>
@@ -21540,7 +21541,7 @@
         <v>-46.4153941</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -21596,7 +21597,7 @@
         <v>-46.4171725</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>117</v>
       </c>
@@ -21652,7 +21653,7 @@
         <v>-46.4164241</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>117</v>
       </c>
@@ -21708,7 +21709,7 @@
         <v>-46.4165888</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>117</v>
       </c>
@@ -21764,7 +21765,7 @@
         <v>-46.415878399999997</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>117</v>
       </c>
@@ -21820,7 +21821,7 @@
         <v>-46.417214999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>165</v>
       </c>
@@ -21876,7 +21877,7 @@
         <v>-46.394514126473538</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>165</v>
       </c>
@@ -21932,7 +21933,7 @@
         <v>-46.39440497485721</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>165</v>
       </c>
@@ -21988,7 +21989,7 @@
         <v>-46.394190685187283</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>165</v>
       </c>
@@ -22044,7 +22045,7 @@
         <v>-46.393867676588513</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>165</v>
       </c>
@@ -22100,7 +22101,7 @@
         <v>-46.393750908484463</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>165</v>
       </c>
@@ -22156,7 +22157,7 @@
         <v>-46.393754824461297</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -22212,7 +22213,7 @@
         <v>-46.393677744048787</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>165</v>
       </c>
@@ -22268,7 +22269,7 @@
         <v>-46.393669850604603</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>165</v>
       </c>
@@ -22324,7 +22325,7 @@
         <v>-46.393617999096797</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>165</v>
       </c>
@@ -22380,7 +22381,7 @@
         <v>-46.39342680270682</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>165</v>
       </c>
@@ -22436,7 +22437,7 @@
         <v>-46.393118667987821</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>165</v>
       </c>
@@ -22492,7 +22493,7 @@
         <v>-46.392683603256813</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>165</v>
       </c>
@@ -22548,7 +22549,7 @@
         <v>-46.392567097741733</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>165</v>
       </c>
@@ -22604,7 +22605,7 @@
         <v>-46.392172750576698</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>165</v>
       </c>
@@ -22660,7 +22661,7 @@
         <v>-46.391704600778667</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>165</v>
       </c>
@@ -22716,7 +22717,7 @@
         <v>-46.393984483001361</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>165</v>
       </c>
@@ -22772,7 +22773,7 @@
         <v>-46.39421417616888</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>165</v>
       </c>
@@ -22828,7 +22829,7 @@
         <v>-46.393884994376727</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>165</v>
       </c>
@@ -22884,7 +22885,7 @@
         <v>-46.393931783273203</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>165</v>
       </c>
@@ -22940,7 +22941,7 @@
         <v>-46.393826949732833</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>165</v>
       </c>
@@ -22996,7 +22997,7 @@
         <v>-46.393834080493427</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>165</v>
       </c>
@@ -23052,7 +23053,7 @@
         <v>-46.393874814521602</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>165</v>
       </c>
@@ -23108,7 +23109,7 @@
         <v>-46.393600080891758</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>165</v>
       </c>
@@ -23164,7 +23165,7 @@
         <v>-46.392812880408918</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>165</v>
       </c>
@@ -23220,7 +23221,7 @@
         <v>-46.392828108924483</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>165</v>
       </c>
@@ -23276,7 +23277,7 @@
         <v>-46.392669018473534</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>165</v>
       </c>
@@ -23332,7 +23333,7 @@
         <v>-46.3922548189284</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>165</v>
       </c>
@@ -23388,7 +23389,7 @@
         <v>-46.391867207322441</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>221</v>
       </c>
@@ -23441,7 +23442,7 @@
         <v>-46.385538400000002</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>221</v>
       </c>
@@ -23494,7 +23495,7 @@
         <v>-46.385575299999999</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>221</v>
       </c>
@@ -23547,7 +23548,7 @@
         <v>-46.385641</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>221</v>
       </c>
@@ -23600,7 +23601,7 @@
         <v>-46.386125</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>221</v>
       </c>
@@ -23653,7 +23654,7 @@
         <v>-46.386338700000003</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>221</v>
       </c>
@@ -23706,7 +23707,7 @@
         <v>-46.387470700000002</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>221</v>
       </c>
@@ -23759,7 +23760,7 @@
         <v>-46.3881558</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>221</v>
       </c>
@@ -23812,7 +23813,7 @@
         <v>-46.3889292</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>221</v>
       </c>
@@ -23865,7 +23866,7 @@
         <v>-46.386140400000002</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>221</v>
       </c>
@@ -23918,7 +23919,7 @@
         <v>-46.386125</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>221</v>
       </c>
@@ -23971,7 +23972,7 @@
         <v>-46.386821400000002</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>221</v>
       </c>
@@ -24021,7 +24022,7 @@
         <v>-46.388970100000002</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>240</v>
       </c>
@@ -24077,7 +24078,7 @@
         <v>-46.400490900000001</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>240</v>
       </c>
@@ -24133,7 +24134,7 @@
         <v>-46.400497299999998</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>240</v>
       </c>
@@ -24189,7 +24190,7 @@
         <v>-46.399660099999998</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>240</v>
       </c>
@@ -24245,7 +24246,7 @@
         <v>-46.399546600000001</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>240</v>
       </c>
@@ -24301,7 +24302,7 @@
         <v>-46.399546899999997</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>240</v>
       </c>
@@ -24357,7 +24358,7 @@
         <v>-46.399427899999999</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>240</v>
       </c>
@@ -24413,7 +24414,7 @@
         <v>-46.399406300000003</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>240</v>
       </c>
@@ -24469,7 +24470,7 @@
         <v>-46.3993976</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>240</v>
       </c>
@@ -24525,7 +24526,7 @@
         <v>-46.399673499999999</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>240</v>
       </c>
@@ -24581,7 +24582,7 @@
         <v>-46.3991951</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>240</v>
       </c>
@@ -24637,7 +24638,7 @@
         <v>-46.3992</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>240</v>
       </c>
@@ -24693,7 +24694,7 @@
         <v>-46.399129500000001</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>240</v>
       </c>
@@ -24749,7 +24750,7 @@
         <v>-46.399120400000001</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -24805,7 +24806,7 @@
         <v>-46.399127700000001</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>240</v>
       </c>
@@ -24861,7 +24862,7 @@
         <v>-46.399663099999998</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>240</v>
       </c>
@@ -24917,7 +24918,7 @@
         <v>-46.399161700000001</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>240</v>
       </c>
@@ -24973,7 +24974,7 @@
         <v>-46.399083099999999</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>240</v>
       </c>
@@ -25029,7 +25030,7 @@
         <v>-46.399065800000002</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>240</v>
       </c>
@@ -25085,7 +25086,7 @@
         <v>-46.399676200000002</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>240</v>
       </c>
@@ -25141,7 +25142,7 @@
         <v>-46.399061099999997</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>240</v>
       </c>
@@ -25197,7 +25198,7 @@
         <v>-46.398950800000001</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>240</v>
       </c>
@@ -25253,7 +25254,7 @@
         <v>-46.3990565</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>240</v>
       </c>
@@ -25309,7 +25310,7 @@
         <v>-46.3990103</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>240</v>
       </c>
@@ -25365,7 +25366,7 @@
         <v>-46.398947300000003</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>280</v>
       </c>
@@ -25418,7 +25419,7 @@
         <v>-46.388409799999998</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>280</v>
       </c>
@@ -25471,7 +25472,7 @@
         <v>-46.386588699999997</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>280</v>
       </c>
@@ -25524,7 +25525,7 @@
         <v>-46.3864564</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>280</v>
       </c>
@@ -25577,7 +25578,7 @@
         <v>-46.387386399999997</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>280</v>
       </c>
@@ -25630,7 +25631,7 @@
         <v>-46.387402899999998</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>280</v>
       </c>
@@ -25683,7 +25684,7 @@
         <v>-46.3874511</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>280</v>
       </c>
@@ -25736,7 +25737,7 @@
         <v>-46.386536300000003</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>280</v>
       </c>
@@ -25789,7 +25790,7 @@
         <v>-46.3952478</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>280</v>
       </c>
@@ -25842,7 +25843,7 @@
         <v>-46.395421599999999</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>280</v>
       </c>
@@ -25895,7 +25896,7 @@
         <v>-46.395309099999999</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>280</v>
       </c>
@@ -25948,7 +25949,7 @@
         <v>-46.3922934</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>280</v>
       </c>
@@ -26001,7 +26002,7 @@
         <v>-46.3922934</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>280</v>
       </c>
@@ -26054,7 +26055,7 @@
         <v>-46.391816499999997</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>280</v>
       </c>
@@ -26107,7 +26108,7 @@
         <v>-46.391055199999997</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>280</v>
       </c>
@@ -26160,7 +26161,7 @@
         <v>-46.390884300000003</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>280</v>
       </c>
@@ -26213,7 +26214,7 @@
         <v>-46.3907059</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>280</v>
       </c>
@@ -26266,7 +26267,7 @@
         <v>-46.389563600000002</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>280</v>
       </c>
@@ -26319,7 +26320,7 @@
         <v>-46.389226299999997</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>280</v>
       </c>
@@ -26372,7 +26373,7 @@
         <v>-46.388674999999999</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>280</v>
       </c>
@@ -26425,7 +26426,7 @@
         <v>-46.388370600000002</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>280</v>
       </c>
@@ -26478,7 +26479,7 @@
         <v>-46.388409799999998</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>280</v>
       </c>
@@ -26531,7 +26532,7 @@
         <v>-46.387695999999998</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>280</v>
       </c>
@@ -26584,7 +26585,7 @@
         <v>-46.387413700000003</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>280</v>
       </c>
@@ -26637,7 +26638,7 @@
         <v>-46.387386399999997</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>280</v>
       </c>
@@ -26690,7 +26691,7 @@
         <v>-46.387402899999998</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>280</v>
       </c>
@@ -26743,7 +26744,7 @@
         <v>-46.386888200000001</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>280</v>
       </c>
@@ -26796,7 +26797,7 @@
         <v>-46.386210499999997</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>280</v>
       </c>
@@ -26849,7 +26850,7 @@
         <v>-46.386560500000002</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>280</v>
       </c>
@@ -26902,7 +26903,7 @@
         <v>-46.392178299999998</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>280</v>
       </c>
@@ -26955,7 +26956,7 @@
         <v>-46.394682400000001</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>280</v>
       </c>
@@ -27008,7 +27009,7 @@
         <v>-46.393901100000001</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>280</v>
       </c>
@@ -27061,7 +27062,7 @@
         <v>-46.393103199999999</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>280</v>
       </c>
@@ -27114,7 +27115,7 @@
         <v>-46.395246</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>280</v>
       </c>
@@ -27167,7 +27168,7 @@
         <v>-46.390622299999997</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>280</v>
       </c>
@@ -27220,7 +27221,7 @@
         <v>-46.388130599999997</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>305</v>
       </c>
@@ -27273,7 +27274,7 @@
         <v>-46.406078299999997</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>305</v>
       </c>
@@ -27326,7 +27327,7 @@
         <v>-46.406567000000003</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>305</v>
       </c>
@@ -27379,7 +27380,7 @@
         <v>-46.407268500000001</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>305</v>
       </c>
@@ -27432,7 +27433,7 @@
         <v>-46.407628899999999</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>305</v>
       </c>
@@ -27485,7 +27486,7 @@
         <v>-46.4079087</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>305</v>
       </c>
@@ -27538,7 +27539,7 @@
         <v>-46.406060400000001</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>305</v>
       </c>
@@ -27591,7 +27592,7 @@
         <v>-46.408232599999998</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>305</v>
       </c>
@@ -27644,7 +27645,7 @@
         <v>-46.408232599999998</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>305</v>
       </c>
@@ -27697,7 +27698,7 @@
         <v>-46.406567000000003</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>305</v>
       </c>
@@ -27750,7 +27751,7 @@
         <v>-46.407268500000001</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>305</v>
       </c>
@@ -27803,7 +27804,7 @@
         <v>-46.406331600000001</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>305</v>
       </c>
@@ -27856,7 +27857,7 @@
         <v>-46.406856099999999</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>312</v>
       </c>
@@ -27903,7 +27904,7 @@
         <v>-46.399636800000003</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>312</v>
       </c>
@@ -27950,7 +27951,7 @@
         <v>-46.399317199999999</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>312</v>
       </c>
@@ -27997,7 +27998,7 @@
         <v>-46.398956400000003</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>312</v>
       </c>
@@ -28044,7 +28045,7 @@
         <v>-46.398719900000003</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>312</v>
       </c>
@@ -28091,7 +28092,7 @@
         <v>-46.398701299999999</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>312</v>
       </c>
@@ -28138,7 +28139,7 @@
         <v>-46.398651000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>312</v>
       </c>
@@ -28185,7 +28186,7 @@
         <v>-46.398395800000003</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>312</v>
       </c>
@@ -28232,7 +28233,7 @@
         <v>-46.397748900000003</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>312</v>
       </c>
@@ -28279,7 +28280,7 @@
         <v>-46.397582200000002</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>312</v>
       </c>
@@ -28326,7 +28327,7 @@
         <v>-46.397804000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>312</v>
       </c>
@@ -28373,7 +28374,7 @@
         <v>-46.398719900000003</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>312</v>
       </c>
@@ -28420,7 +28421,7 @@
         <v>-46.3982283</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>312</v>
       </c>
@@ -28467,7 +28468,7 @@
         <v>-46.3982283</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>312</v>
       </c>
@@ -28514,7 +28515,7 @@
         <v>-46.398651000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>312</v>
       </c>
@@ -28561,7 +28562,7 @@
         <v>-46.397804000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>317</v>
       </c>
@@ -28614,7 +28615,7 @@
         <v>-46.395039500000003</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>317</v>
       </c>
@@ -28667,7 +28668,7 @@
         <v>-46.399920799999997</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>317</v>
       </c>
@@ -28720,7 +28721,7 @@
         <v>-46.399732299999997</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>317</v>
       </c>
@@ -28773,7 +28774,7 @@
         <v>-46.402293800000002</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>317</v>
       </c>
@@ -28826,7 +28827,7 @@
         <v>-46.401741199999996</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>317</v>
       </c>
@@ -28879,7 +28880,7 @@
         <v>-46.4013214</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>317</v>
       </c>
@@ -28932,7 +28933,7 @@
         <v>-46.400779200000002</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>317</v>
       </c>
@@ -28985,7 +28986,7 @@
         <v>-46.400237500000003</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>317</v>
       </c>
@@ -29038,7 +29039,7 @@
         <v>-46.400053399999997</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>317</v>
       </c>
@@ -29091,7 +29092,7 @@
         <v>-46.397993399999997</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>317</v>
       </c>
@@ -29144,7 +29145,7 @@
         <v>-46.3980842</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>317</v>
       </c>
@@ -29197,7 +29198,7 @@
         <v>-46.398204</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>317</v>
       </c>
@@ -29250,7 +29251,7 @@
         <v>-46.398731099999999</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>317</v>
       </c>
@@ -29303,7 +29304,7 @@
         <v>-46.398578299999997</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>317</v>
       </c>
@@ -29356,7 +29357,7 @@
         <v>-46.399111300000001</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>317</v>
       </c>
@@ -29409,7 +29410,7 @@
         <v>-46.399396500000002</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>317</v>
       </c>
@@ -29462,7 +29463,7 @@
         <v>-46.3996371</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>317</v>
       </c>
@@ -29515,7 +29516,7 @@
         <v>-46.399732299999997</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>317</v>
       </c>
@@ -29568,7 +29569,7 @@
         <v>-46.397703300000003</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>317</v>
       </c>
@@ -29621,7 +29622,7 @@
         <v>-46.397365899999997</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>317</v>
       </c>
@@ -29674,7 +29675,7 @@
         <v>-46.396937700000002</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>317</v>
       </c>
@@ -29727,7 +29728,7 @@
         <v>-46.396631800000002</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>317</v>
       </c>
@@ -29780,7 +29781,7 @@
         <v>-46.396280500000003</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>317</v>
       </c>
@@ -29833,7 +29834,7 @@
         <v>-46.395845000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>317</v>
       </c>
@@ -29886,7 +29887,7 @@
         <v>-46.395425600000003</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>317</v>
       </c>
@@ -29939,7 +29940,7 @@
         <v>-46.395425600000003</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>317</v>
       </c>
@@ -29992,7 +29993,7 @@
         <v>-46.393717500000001</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>317</v>
       </c>
@@ -30045,7 +30046,7 @@
         <v>-46.393569399999997</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>317</v>
       </c>
@@ -30098,7 +30099,7 @@
         <v>-46.393071999999997</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>317</v>
       </c>
@@ -30151,7 +30152,7 @@
         <v>-46.392376200000001</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>317</v>
       </c>
@@ -30204,7 +30205,7 @@
         <v>-46.3960948</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>317</v>
       </c>
@@ -30257,7 +30258,7 @@
         <v>-46.398731099999999</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>317</v>
       </c>
@@ -30310,7 +30311,7 @@
         <v>-46.4022632</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>317</v>
       </c>
@@ -30363,7 +30364,7 @@
         <v>-46.395845000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>317</v>
       </c>
@@ -30416,7 +30417,7 @@
         <v>-46.3960948</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>317</v>
       </c>
@@ -30469,7 +30470,7 @@
         <v>-46.396000600000001</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>317</v>
       </c>
@@ -30522,7 +30523,7 @@
         <v>-46.395630199999999</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>317</v>
       </c>
@@ -30575,7 +30576,7 @@
         <v>-46.397993399999997</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>317</v>
       </c>
@@ -30628,7 +30629,7 @@
         <v>-46.397993399999997</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>317</v>
       </c>
@@ -30681,7 +30682,7 @@
         <v>-46.397979200000002</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>317</v>
       </c>
@@ -30734,7 +30735,7 @@
         <v>-46.3980842</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>317</v>
       </c>
@@ -30784,7 +30785,7 @@
         <v>-46.398089400000003</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>317</v>
       </c>
@@ -30837,7 +30838,7 @@
         <v>-46.392376200000001</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>317</v>
       </c>
@@ -30890,7 +30891,7 @@
         <v>-46.390559500000002</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>317</v>
       </c>
@@ -30943,7 +30944,7 @@
         <v>-46.391169300000001</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>317</v>
       </c>
@@ -30996,7 +30997,7 @@
         <v>-46.391454299999999</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>317</v>
       </c>
@@ -31049,7 +31050,7 @@
         <v>-46.391380099999999</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>317</v>
       </c>
@@ -31102,7 +31103,7 @@
         <v>-46.392123900000001</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>317</v>
       </c>
@@ -31155,7 +31156,7 @@
         <v>-46.391454400000001</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>317</v>
       </c>
@@ -31208,7 +31209,7 @@
         <v>-46.391457500000001</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>317</v>
       </c>
@@ -31261,7 +31262,7 @@
         <v>-46.390500799999998</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>317</v>
       </c>
@@ -31314,7 +31315,7 @@
         <v>-46.390509799999997</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>317</v>
       </c>
@@ -31367,7 +31368,7 @@
         <v>-46.391380099999999</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>317</v>
       </c>
@@ -31420,7 +31421,7 @@
         <v>-46.390866699999997</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>317</v>
       </c>
@@ -31473,7 +31474,7 @@
         <v>-46.390534500000001</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>317</v>
       </c>
@@ -31526,7 +31527,7 @@
         <v>-46.391384500000001</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>352</v>
       </c>
@@ -31579,7 +31580,7 @@
         <v>-46.392097399999997</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>352</v>
       </c>
@@ -31632,7 +31633,7 @@
         <v>-46.391953299999997</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>352</v>
       </c>
@@ -31685,7 +31686,7 @@
         <v>-46.391780500000003</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>352</v>
       </c>
@@ -31738,7 +31739,7 @@
         <v>-46.392170900000004</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>352</v>
       </c>
@@ -31791,7 +31792,7 @@
         <v>-46.392086900000002</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>352</v>
       </c>
@@ -31844,7 +31845,7 @@
         <v>-46.392177699999998</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>352</v>
       </c>
@@ -31897,7 +31898,7 @@
         <v>-46.392434799999997</v>
       </c>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>352</v>
       </c>
@@ -31950,7 +31951,7 @@
         <v>-46.3926789</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>352</v>
       </c>
@@ -32003,7 +32004,7 @@
         <v>-46.392434799999997</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>352</v>
       </c>
@@ -32056,7 +32057,7 @@
         <v>-46.392170900000004</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>352</v>
       </c>
@@ -32109,7 +32110,7 @@
         <v>-46.391780500000003</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>352</v>
       </c>
@@ -32162,7 +32163,7 @@
         <v>-46.392123900000001</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>352</v>
       </c>
@@ -32215,7 +32216,7 @@
         <v>-46.392097399999997</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>352</v>
       </c>
@@ -32268,7 +32269,7 @@
         <v>-46.391780699999998</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>355</v>
       </c>
@@ -32321,7 +32322,7 @@
         <v>-46.391734700000001</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>355</v>
       </c>
@@ -32374,7 +32375,7 @@
         <v>-46.391399900000003</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>355</v>
       </c>
@@ -32427,7 +32428,7 @@
         <v>-46.390832000000003</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>355</v>
       </c>
@@ -32480,7 +32481,7 @@
         <v>-46.390766499999998</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>355</v>
       </c>
@@ -32533,7 +32534,7 @@
         <v>-46.390832000000003</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>355</v>
       </c>
@@ -32586,7 +32587,7 @@
         <v>-46.390613000000002</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>355</v>
       </c>
@@ -32639,7 +32640,7 @@
         <v>-46.390234300000003</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>355</v>
       </c>
@@ -32692,7 +32693,7 @@
         <v>-46.389846900000002</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>355</v>
       </c>
@@ -32745,7 +32746,7 @@
         <v>-46.3894801</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>355</v>
       </c>
@@ -32798,7 +32799,7 @@
         <v>-46.389092400000003</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>355</v>
       </c>
@@ -32851,7 +32852,7 @@
         <v>-46.388676799999999</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>355</v>
       </c>
@@ -32904,7 +32905,7 @@
         <v>-46.386397299999999</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>355</v>
       </c>
@@ -32957,7 +32958,7 @@
         <v>-46.387154600000002</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>355</v>
       </c>
@@ -33010,7 +33011,7 @@
         <v>-46.3879375</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>355</v>
       </c>
@@ -33063,7 +33064,7 @@
         <v>-46.3859675</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>355</v>
       </c>
@@ -33116,7 +33117,7 @@
         <v>-46.3862132</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>355</v>
       </c>
@@ -33169,7 +33170,7 @@
         <v>-46.3863129</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>355</v>
       </c>
@@ -33222,7 +33223,7 @@
         <v>-46.386583299999998</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>355</v>
       </c>
@@ -33275,7 +33276,7 @@
         <v>-46.392179599999999</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>355</v>
       </c>
@@ -33328,7 +33329,7 @@
         <v>-46.388432899999998</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>355</v>
       </c>
@@ -33381,7 +33382,7 @@
         <v>-46.388676799999999</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>363</v>
       </c>
@@ -33434,7 +33435,7 @@
         <v>-46.397681599999999</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>363</v>
       </c>
@@ -33487,7 +33488,7 @@
         <v>-46.3974324</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>363</v>
       </c>
@@ -33540,7 +33541,7 @@
         <v>-46.396907200000001</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>363</v>
       </c>
@@ -33593,7 +33594,7 @@
         <v>-46.396283199999999</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>363</v>
       </c>
@@ -33646,7 +33647,7 @@
         <v>-46.396234700000001</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>363</v>
       </c>
@@ -33699,7 +33700,7 @@
         <v>-46.396234700000001</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>363</v>
       </c>
@@ -33752,7 +33753,7 @@
         <v>-46.395672300000001</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>363</v>
       </c>
@@ -33805,7 +33806,7 @@
         <v>-46.394411300000002</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>363</v>
       </c>
@@ -33858,7 +33859,7 @@
         <v>-46.393959799999998</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>363</v>
       </c>
@@ -33911,7 +33912,7 @@
         <v>-46.3936408</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>363</v>
       </c>
@@ -33964,7 +33965,7 @@
         <v>-46.393255099999998</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>363</v>
       </c>
@@ -34017,7 +34018,7 @@
         <v>-46.396111300000001</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>363</v>
       </c>
@@ -34070,7 +34071,7 @@
         <v>-46.395125499999999</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>363</v>
       </c>
@@ -34123,7 +34124,7 @@
         <v>-46.397876199999999</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>363</v>
       </c>
@@ -34176,7 +34177,7 @@
         <v>-46.394917599999999</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>363</v>
       </c>
@@ -34229,7 +34230,7 @@
         <v>-46.394633800000001</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>363</v>
       </c>
@@ -34282,7 +34283,7 @@
         <v>-46.392941700000002</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>363</v>
       </c>
@@ -34335,7 +34336,7 @@
         <v>-46.390125500000003</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>363</v>
       </c>
@@ -34388,7 +34389,7 @@
         <v>-46.390125500000003</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>363</v>
       </c>
@@ -34441,7 +34442,7 @@
         <v>-46.389316899999997</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>363</v>
       </c>
@@ -34494,7 +34495,7 @@
         <v>-46.388850499999997</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>363</v>
       </c>
@@ -34547,7 +34548,7 @@
         <v>-46.388869300000003</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>363</v>
       </c>
@@ -34600,7 +34601,7 @@
         <v>-46.388991099999998</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>363</v>
       </c>
@@ -34653,7 +34654,7 @@
         <v>-46.389474800000002</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>363</v>
       </c>
@@ -34706,7 +34707,7 @@
         <v>-46.389775499999999</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>363</v>
       </c>
@@ -34759,7 +34760,7 @@
         <v>-46.3911503</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>363</v>
       </c>
@@ -34812,7 +34813,7 @@
         <v>-46.390674300000001</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>363</v>
       </c>
@@ -34865,7 +34866,7 @@
         <v>-46.390674300000001</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>363</v>
       </c>
@@ -34918,7 +34919,7 @@
         <v>-46.390674300000001</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>363</v>
       </c>
@@ -34971,7 +34972,7 @@
         <v>-46.390125500000003</v>
       </c>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>363</v>
       </c>
@@ -35024,7 +35025,7 @@
         <v>-46.3936408</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>363</v>
       </c>
@@ -35077,7 +35078,7 @@
         <v>-46.392461500000003</v>
       </c>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>363</v>
       </c>
@@ -35130,7 +35131,7 @@
         <v>-46.392190599999999</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>363</v>
       </c>
@@ -35183,7 +35184,7 @@
         <v>-46.391619599999999</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>363</v>
       </c>
@@ -35236,7 +35237,7 @@
         <v>-46.392941700000002</v>
       </c>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>363</v>
       </c>
@@ -35289,7 +35290,7 @@
         <v>-46.389474800000002</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>363</v>
       </c>
@@ -35342,7 +35343,7 @@
         <v>-46.393255099999998</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>363</v>
       </c>
@@ -35395,7 +35396,7 @@
         <v>-46.393256299999997</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>363</v>
       </c>
@@ -35448,7 +35449,7 @@
         <v>-46.393255099999998</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>363</v>
       </c>
@@ -35501,7 +35502,7 @@
         <v>-46.392941700000002</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>363</v>
       </c>
@@ -35554,7 +35555,7 @@
         <v>-46.392921100000002</v>
       </c>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>363</v>
       </c>
@@ -35607,7 +35608,7 @@
         <v>-46.392921100000002</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>377</v>
       </c>
@@ -35660,7 +35661,7 @@
         <v>-46.399263099999999</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>377</v>
       </c>
@@ -35713,7 +35714,7 @@
         <v>-46.400001500000002</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>377</v>
       </c>
@@ -35766,7 +35767,7 @@
         <v>-46.400030800000003</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>377</v>
       </c>
@@ -35819,7 +35820,7 @@
         <v>-46.398584399999997</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>377</v>
       </c>
@@ -35872,7 +35873,7 @@
         <v>-46.399263099999999</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>377</v>
       </c>
@@ -35925,7 +35926,7 @@
         <v>-46.399334099999997</v>
       </c>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>377</v>
       </c>
@@ -35978,7 +35979,7 @@
         <v>-46.399334099999997</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>377</v>
       </c>
@@ -36031,7 +36032,7 @@
         <v>-46.398702299999997</v>
       </c>
     </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>377</v>
       </c>
@@ -36084,7 +36085,7 @@
         <v>-46.398688399999998</v>
       </c>
     </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>377</v>
       </c>
@@ -36137,7 +36138,7 @@
         <v>-46.398706799999999</v>
       </c>
     </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>377</v>
       </c>
@@ -36190,7 +36191,7 @@
         <v>-46.398702299999997</v>
       </c>
     </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>377</v>
       </c>
@@ -36243,7 +36244,7 @@
         <v>-46.400631799999999</v>
       </c>
     </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>377</v>
       </c>
@@ -36296,7 +36297,7 @@
         <v>-46.401348900000002</v>
       </c>
     </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>377</v>
       </c>
@@ -36337,7 +36338,7 @@
         <v>-46.401348900000002</v>
       </c>
     </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>377</v>
       </c>
@@ -36378,7 +36379,7 @@
         <v>-46.401776300000002</v>
       </c>
     </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>377</v>
       </c>
@@ -36419,7 +36420,7 @@
         <v>-46.401348900000002</v>
       </c>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>377</v>
       </c>
@@ -36472,7 +36473,7 @@
         <v>-46.401958399999998</v>
       </c>
     </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>377</v>
       </c>
@@ -36525,7 +36526,7 @@
         <v>-46.402794299999996</v>
       </c>
     </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>377</v>
       </c>
@@ -36578,7 +36579,7 @@
         <v>-46.402279700000001</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>377</v>
       </c>
@@ -36631,7 +36632,7 @@
         <v>-46.402184699999999</v>
       </c>
     </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>377</v>
       </c>
@@ -36684,7 +36685,7 @@
         <v>-46.402279700000001</v>
       </c>
     </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>377</v>
       </c>
@@ -36737,7 +36738,7 @@
         <v>-46.401958399999998</v>
       </c>
     </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>363</v>
       </c>
@@ -36793,7 +36794,7 @@
         <v>-46.3959507</v>
       </c>
     </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>363</v>
       </c>
@@ -36849,7 +36850,7 @@
         <v>-46.396032599999998</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>388</v>
       </c>
@@ -36905,7 +36906,7 @@
         <v>-46.385066799999997</v>
       </c>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>388</v>
       </c>
@@ -36961,7 +36962,7 @@
         <v>-46.3856647</v>
       </c>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>388</v>
       </c>
@@ -37017,7 +37018,7 @@
         <v>-46.386281199999999</v>
       </c>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>388</v>
       </c>
@@ -37073,7 +37074,7 @@
         <v>-46.385869399999997</v>
       </c>
     </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>388</v>
       </c>
@@ -37129,7 +37130,7 @@
         <v>-46.385849999999998</v>
       </c>
     </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>165</v>
       </c>
@@ -37185,7 +37186,7 @@
         <v>-46.393826947651448</v>
       </c>
     </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>165</v>
       </c>
@@ -37241,7 +37242,7 @@
         <v>-46.392254815122861</v>
       </c>
     </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>117</v>
       </c>
@@ -37297,7 +37298,7 @@
         <v>-46.4176511</v>
       </c>
     </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>117</v>
       </c>
@@ -37353,7 +37354,7 @@
         <v>-46.415050600000001</v>
       </c>
     </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>117</v>
       </c>
@@ -37409,7 +37410,7 @@
         <v>-46.416166400000002</v>
       </c>
     </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>117</v>
       </c>
@@ -37659,7 +37660,7 @@
         <v>530</v>
       </c>
       <c r="I367">
-        <v>88.66</v>
+        <v>0</v>
       </c>
       <c r="J367">
         <v>7.38</v>
@@ -37745,7 +37746,7 @@
         <v>-46.401156800000003</v>
       </c>
     </row>
-    <row r="369" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>363</v>
       </c>
@@ -37801,7 +37802,7 @@
         <v>-46.396509199999997</v>
       </c>
     </row>
-    <row r="370" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>363</v>
       </c>
@@ -37857,7 +37858,7 @@
         <v>-46.396530900000002</v>
       </c>
     </row>
-    <row r="371" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>421</v>
       </c>
@@ -37913,7 +37914,7 @@
         <v>-46.388130599999997</v>
       </c>
     </row>
-    <row r="372" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>421</v>
       </c>
@@ -37969,7 +37970,7 @@
         <v>-46.388117800000003</v>
       </c>
     </row>
-    <row r="373" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>421</v>
       </c>
@@ -38025,7 +38026,7 @@
         <v>-46.388055299999998</v>
       </c>
     </row>
-    <row r="374" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>421</v>
       </c>
@@ -38081,7 +38082,7 @@
         <v>-46.3875758</v>
       </c>
     </row>
-    <row r="375" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>421</v>
       </c>
@@ -38137,7 +38138,7 @@
         <v>-46.387807600000002</v>
       </c>
     </row>
-    <row r="376" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>421</v>
       </c>
@@ -38193,7 +38194,7 @@
         <v>-46.388296699999998</v>
       </c>
     </row>
-    <row r="377" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>421</v>
       </c>
@@ -38249,7 +38250,7 @@
         <v>-46.388917999999997</v>
       </c>
     </row>
-    <row r="378" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>421</v>
       </c>
@@ -38305,7 +38306,7 @@
         <v>-46.389496999999999</v>
       </c>
     </row>
-    <row r="379" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>421</v>
       </c>
@@ -38361,7 +38362,7 @@
         <v>-46.390075299999999</v>
       </c>
     </row>
-    <row r="380" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>421</v>
       </c>
@@ -38417,7 +38418,7 @@
         <v>-46.390118399999999</v>
       </c>
     </row>
-    <row r="381" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>421</v>
       </c>
@@ -38473,7 +38474,7 @@
         <v>-46.388296699999998</v>
       </c>
     </row>
-    <row r="382" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>439</v>
       </c>
@@ -38529,7 +38530,7 @@
         <v>-46.416035000000001</v>
       </c>
     </row>
-    <row r="383" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>439</v>
       </c>
@@ -38585,7 +38586,7 @@
         <v>-46.416319799999997</v>
       </c>
     </row>
-    <row r="384" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>439</v>
       </c>
@@ -38641,7 +38642,7 @@
         <v>-46.4161942</v>
       </c>
     </row>
-    <row r="385" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>439</v>
       </c>
@@ -38697,7 +38698,7 @@
         <v>-46.416128800000003</v>
       </c>
     </row>
-    <row r="386" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>439</v>
       </c>
@@ -38753,7 +38754,7 @@
         <v>-46.416162700000001</v>
       </c>
     </row>
-    <row r="387" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>439</v>
       </c>
@@ -38809,7 +38810,7 @@
         <v>-46.416152199999999</v>
       </c>
     </row>
-    <row r="388" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>439</v>
       </c>
@@ -38866,7 +38867,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R388" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="A1:R388" xr:uid="{00000000-0001-0000-0300-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="conceicao"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/doc/docs/planilha_base_mapa.xlsx
+++ b/doc/docs/planilha_base_mapa.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L381"/>
+  <dimension ref="A1:L383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18385,6 +18385,102 @@
       <c r="L381" t="inlineStr">
         <is>
           <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>JC-PV-09</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>PV-09</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>7396914.814</v>
+      </c>
+      <c r="F382" t="n">
+        <v>358382.74</v>
+      </c>
+      <c r="G382" t="n">
+        <v>-23.5318788</v>
+      </c>
+      <c r="H382" t="n">
+        <v>-46.3872832</v>
+      </c>
+      <c r="I382" t="n">
+        <v>768.775</v>
+      </c>
+      <c r="J382" t="n">
+        <v>766.275</v>
+      </c>
+      <c r="K382" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-03/FL-04 versao 01, 11.MAI.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>JC-PV-10</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>PV-10</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>7396932.164</v>
+      </c>
+      <c r="F383" t="n">
+        <v>358437.094</v>
+      </c>
+      <c r="G383" t="n">
+        <v>-23.5317269</v>
+      </c>
+      <c r="H383" t="n">
+        <v>-46.3867492</v>
+      </c>
+      <c r="I383" t="n">
+        <v>770.008</v>
+      </c>
+      <c r="J383" t="n">
+        <v>767.008</v>
+      </c>
+      <c r="K383" t="n">
+        <v>3</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-04 versao 01, 11.MAI.2026</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R401"/>
+  <dimension ref="A1:R403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -46599,6 +46695,154 @@
       </c>
       <c r="R401" t="n">
         <v>-46.416679</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>JC-003</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>PV-08 - PV-09</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>PV-08</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>PV-09</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>355</v>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I402" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="J402" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K402" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L402" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>em planejamento</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-03 versao 01, 11.MAI.2026; GALPAO INTERNO RUA GENI GOMES; taxa 0,0311.</t>
+        </is>
+      </c>
+      <c r="O402" t="n">
+        <v>-23.5320183</v>
+      </c>
+      <c r="P402" t="n">
+        <v>-46.3877736</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>-23.5318788</v>
+      </c>
+      <c r="R402" t="n">
+        <v>-46.3872832</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>JC-004</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>PV-09 - PV-10</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>PV-09</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>PV-10</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>355</v>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I403" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="J403" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K403" t="n">
+        <v>3</v>
+      </c>
+      <c r="L403" t="n">
+        <v>3</v>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>em planejamento</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-04 versao 01, 11.MAI.2026; GALPAO INTERNO RUA GENI GOMES; taxa 0,0129.</t>
+        </is>
+      </c>
+      <c r="O403" t="n">
+        <v>-23.5318788</v>
+      </c>
+      <c r="P403" t="n">
+        <v>-46.3872832</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>-23.5317269</v>
+      </c>
+      <c r="R403" t="n">
+        <v>-46.3867492</v>
       </c>
     </row>
   </sheetData>
